--- a/input/наличие.xlsx
+++ b/input/наличие.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YD\YandexDisk\Originall\Parse — playwright\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{480DD395-217D-483E-A8C4-9EB9DC28D2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{838E12AA-6965-4DA1-A421-AD90C187E140}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{37A2491E-F95C-40AF-B0C1-7262A776B8A2}"/>
   </bookViews>

--- a/input/наличие.xlsx
+++ b/input/наличие.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Парсинг Весов\Вход\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YD\YandexDisk\Originall\Parse -old\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B0CAEBF-7A82-4129-8C07-99BE35A7B7AC}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A576C5-0418-4CEB-8CF8-D3B10AB9CD25}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15255" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1206,7 +1206,7 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1437,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="C26">
-        <v>16</v>
+        <v>800</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1558,7 +1558,7 @@
         <v>1</v>
       </c>
       <c r="C37">
-        <v>16</v>
+        <v>699</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -1866,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="C65">
-        <v>93</v>
+        <v>500</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1987,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="C76">
-        <v>39</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
